--- a/batchstudent/Result/anlpvhe187047/OverallSummary.xlsx
+++ b/batchstudent/Result/anlpvhe187047/OverallSummary.xlsx
@@ -37,25 +37,25 @@
     <x:t>FAIL</x:t>
   </x:si>
   <x:si>
-    <x:t>Network flows: 1 FAIL (ALL-OR-NOTHING), 1 PASS</x:t>
+    <x:t>Network flows: 2 FAIL (ALL-OR-NOTHING), 0 PASS</x:t>
   </x:si>
   <x:si>
     <x:t>TC2</x:t>
   </x:si>
   <x:si>
-    <x:t>Network flows: 2 FAIL (ALL-OR-NOTHING), 1 PASS</x:t>
+    <x:t>Network flows: 3 FAIL (ALL-OR-NOTHING), 0 PASS</x:t>
   </x:si>
   <x:si>
     <x:t>TC3</x:t>
   </x:si>
   <x:si>
-    <x:t>Network flows: 6 FAIL (ALL-OR-NOTHING), 1 PASS</x:t>
+    <x:t>Network flows: 7 FAIL (ALL-OR-NOTHING), 0 PASS</x:t>
   </x:si>
   <x:si>
     <x:t>TC4</x:t>
   </x:si>
   <x:si>
-    <x:t>Network flows: 10 FAIL (ALL-OR-NOTHING), 1 PASS</x:t>
+    <x:t>Network flows: 11 FAIL (ALL-OR-NOTHING), 0 PASS</x:t>
   </x:si>
   <x:si>
     <x:t>TC5</x:t>
@@ -64,7 +64,7 @@
     <x:t>TC6</x:t>
   </x:si>
   <x:si>
-    <x:t>Network flows: 20 FAIL (ALL-OR-NOTHING), 2 PASS</x:t>
+    <x:t>Network flows: 22 FAIL (ALL-OR-NOTHING), 0 PASS</x:t>
   </x:si>
 </x:sst>
 </file>
